--- a/optimisation/code/output_metadata/RosteringANDAllocationANDScheduling1.xlsx
+++ b/optimisation/code/output_metadata/RosteringANDAllocationANDScheduling1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10824"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11214"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://liveuclac-my.sharepoint.com/personal/ucahscr_ucl_ac_uk/Documents/WORKTECC - CORU/Publications/WORKTECC_OR_paper/R_code/optimisation/code/output_metadata/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://liveuclac-my.sharepoint.com/personal/ucahlgr_ucl_ac_uk/Documents/worktecc_modelling_framework/optimisation/code/output_metadata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="36" documentId="11_A0429C1081A4784D1A7D00E9594BBB2F046639E4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ED7C6108-23DE-4739-B826-ADCA0A3A1426}"/>
+  <xr:revisionPtr revIDLastSave="38" documentId="11_A0429C1081A4784D1A7D00E9594BBB2F046639E4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FD143C36-112C-684D-8B86-32A5B883FC70}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="23240" windowHeight="13880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -393,8 +393,8 @@
   <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="29.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="45" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.2">
